--- a/branches/dev/ValueSet-mii-vs-mtb-msi.xlsx
+++ b/branches/dev/ValueSet-mii-vs-mtb-msi.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T04:08:55+00:00</t>
+    <t>2026-09-15T04:40:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-mtb-msi.xlsx
+++ b/branches/dev/ValueSet-mii-vs-mtb-msi.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.0.1</t>
+    <t>2027.0.0-ballot.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T04:40:11+00:00</t>
+    <t>2026-09-15T12:06:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
